--- a/Performance_Tracker.xlsx
+++ b/Performance_Tracker.xlsx
@@ -1,148 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peter\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C73BF59-60A5-4D07-8A29-96ADFE33F8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Contribution Tracker" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contribution Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>TPS_3371_TEAM_20 — Team Contribution &amp; Performance Tracker</t>
-  </si>
-  <si>
-    <t>Team Lead: Peter  |  Score = 0–100 per activity, based on actual participation/contribution  |  Yellow cells = enter scores  |  Column header = Date – Activity Type: Brief description  |  Not an official course grade  |  Keep accurate — instructor reviews repo activity</t>
-  </si>
-  <si>
-    <t>Team Member</t>
-  </si>
-  <si>
-    <t>Sep 13 – Milestone 1: Proposal</t>
-  </si>
-  <si>
-    <t>Sep 14 – In-Class Activity: HTML &amp; GitHub Setup</t>
-  </si>
-  <si>
-    <t>Out-of-Class Activity 1: [description]</t>
-  </si>
-  <si>
-    <t>Milestone 2: [description]</t>
-  </si>
-  <si>
-    <t>In-Class Activity 2: [description]</t>
-  </si>
-  <si>
-    <t>Week 3 Group Activity: Architecture + Responsibility Matrix</t>
-  </si>
-  <si>
-    <t>Milestone 3: [description]</t>
-  </si>
-  <si>
-    <t>Milestone 4: [description]</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>Daja</t>
-  </si>
-  <si>
-    <t>Sophia</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>Yoki</t>
-  </si>
-  <si>
-    <t>Team Average</t>
-  </si>
-  <si>
-    <t>To add a new activity: insert a column before "Average", title it "[Date] – [Type]: [Brief description]" (e.g., "Sep 22 – Out-of-Class: Data Dictionary Draft"), then enter each member's score 0–100.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF555555"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Calibri"/>
       <charset val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,31 +111,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -303,14 +220,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -492,253 +401,211 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="9"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7">
-        <v>100</v>
-      </c>
-      <c r="C5" s="7">
-        <v>100</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8">
-        <f>IFERROR(AVERAGE(B5:I5),"")</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="7">
-        <v>100</v>
-      </c>
-      <c r="C6" s="7">
-        <v>100</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8">
-        <f>IFERROR(AVERAGE(B6:I6),"")</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="7">
-        <v>100</v>
-      </c>
-      <c r="C7" s="7">
-        <v>100</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8">
-        <f>IFERROR(AVERAGE(B7:I7),"")</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="7">
-        <v>100</v>
-      </c>
-      <c r="C8" s="7">
-        <v>100</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8">
-        <f>IFERROR(AVERAGE(B8:I8),"")</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="7">
-        <v>100</v>
-      </c>
-      <c r="C9" s="7">
-        <v>100</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8">
-        <f>IFERROR(AVERAGE(B9:I9),"")</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>17</v>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TPS_3371_TEAM_20 — Team Contribution &amp; Performance Tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Team Lead: Peter  |  Score = 0–100 per activity, based on actual participation/contribution  |  Yellow cells = enter scores  |  Column header = Date – Activity Type: Brief description  |  Not an official course grade  |  Keep accurate — instructor reviews repo activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Team Member</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Milestone 1 (Week 3): Project Proposal</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Week 6 Group Exercise Pack: Team Activity</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Week 6 Group Exercise Pack: Individual Assignment</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="8">
+        <f>IFERROR(AVERAGE(B5:D5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Daja</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="8">
+        <f>IFERROR(AVERAGE(B6:D6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="8">
+        <f>IFERROR(AVERAGE(B7:D7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="8">
+        <f>IFERROR(AVERAGE(B8:D8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Yoki</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="8">
+        <f>IFERROR(AVERAGE(B9:D9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Team Average</t>
+        </is>
       </c>
       <c r="B11" s="10">
-        <f t="shared" ref="B11:J11" si="0">IFERROR(AVERAGE(B5:B9),"")</f>
-        <v>100</v>
+        <f>IFERROR(AVERAGE(B5:B9),"")</f>
+        <v/>
       </c>
       <c r="C11" s="10">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="D11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+        <f>IFERROR(AVERAGE(C5:C9),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="10">
+        <f>IFERROR(AVERAGE(D5:D9),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="10">
+        <f>IFERROR(AVERAGE(E5:E9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>To add a new activity: insert a column before "Average", title it "[Date] – [Type]: [Brief description]" (e.g., "Sep 22 – Out-of-Class: Data Dictionary Draft"), then enter each member's score 0–100.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:I9">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(ISNUMBER(B5),B5&lt;70)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Invalid score" error="Enter a whole number from 0 to 100." sqref="B5:I9" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="B5:I9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid score" error="Enter a whole number from 0 to 100." type="whole">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Performance_Tracker.xlsx
+++ b/Performance_Tracker.xlsx
@@ -112,15 +112,6 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -137,6 +128,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -409,190 +407,189 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="9"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" style="9" min="1" max="1"/>
+    <col width="22" customWidth="1" style="9" min="2" max="2"/>
+    <col width="24" customWidth="1" style="9" min="3" max="3"/>
+    <col width="26" customWidth="1" style="9" min="4" max="4"/>
+    <col width="12" customWidth="1" style="9" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TPS_3371_TEAM_20 — Team Contribution &amp; Performance Tracker</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Team Lead: Peter  |  Score = 0–100 per activity, based on actual participation/contribution  |  Yellow cells = enter scores  |  Column header = Date – Activity Type: Brief description  |  Not an official course grade  |  Keep accurate — instructor reviews repo activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="1" ht="25.5" customHeight="1" s="9">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>TPS_3371_TEAM_20 - Team Contribution &amp; Performance Tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27.75" customHeight="1" s="9">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Team Lead: Peter  |  Score = 0-100 per activity, based on actual participation/contribution  |  Yellow cells = enter scores  |  Column header = Date - Activity Type: Brief description  |  Not an official course grade  |  Keep accurate - instructor reviews repo activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" s="9">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Team Member</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Milestone 1 (Week 3): Project Proposal</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Week 6 Group Exercise Pack: Team Activity</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Week 6 Group Exercise Pack: Individual Assignment</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="B5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="5">
         <f>IFERROR(AVERAGE(B5:D5),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Daja</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="5">
         <f>IFERROR(AVERAGE(B6:D6),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Sophia</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="B7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="5">
         <f>IFERROR(AVERAGE(B7:D7),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Elizabeth</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="B8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="5">
         <f>IFERROR(AVERAGE(B8:D8),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Yoki</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="5">
         <f>IFERROR(AVERAGE(B9:D9),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Team Average</t>
         </is>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <f>IFERROR(AVERAGE(B5:B9),"")</f>
         <v/>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="7">
         <f>IFERROR(AVERAGE(C5:C9),"")</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="7">
         <f>IFERROR(AVERAGE(D5:D9),"")</f>
         <v/>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="7">
         <f>IFERROR(AVERAGE(E5:E9),"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>To add a new activity: insert a column before "Average", title it "[Date] – [Type]: [Brief description]" (e.g., "Sep 22 – Out-of-Class: Data Dictionary Draft"), then enter each member's score 0–100.</t>
+    <row r="13" ht="15" customHeight="1" s="9">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>To add a new activity: insert a column before "Average", title it "[Date] - [Type]: [Brief description]" (e.g., "Sep 22 - Out-of-Class: Data Dictionary Draft"), then enter each member's score 0-100.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:I9">
     <cfRule type="expression" priority="2" dxfId="0">

--- a/Performance_Tracker.xlsx
+++ b/Performance_Tracker.xlsx
@@ -404,14 +404,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="9" min="1" max="1"/>
     <col width="22" customWidth="1" style="9" min="2" max="2"/>
     <col width="24" customWidth="1" style="9" min="3" max="3"/>
     <col width="26" customWidth="1" style="9" min="4" max="4"/>
-    <col width="12" customWidth="1" style="9" min="5" max="5"/>
+    <col width="26" customWidth="1" style="9" min="5" max="5"/>
+    <col width="24" customWidth="1" style="9" min="6" max="6"/>
+    <col width="12" customWidth="1" style="9" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="9">
@@ -420,6 +422,12 @@
           <t>TPS_3371_TEAM_20 - Team Contribution &amp; Performance Tracker</t>
         </is>
       </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="9">
       <c r="A2" s="10" t="inlineStr">
@@ -427,7 +435,14 @@
           <t>Team Lead: Peter  |  Score = 0-100 per activity, based on actual participation/contribution  |  Yellow cells = enter scores  |  Column header = Date - Activity Type: Brief description  |  Not an official course grade  |  Keep accurate - instructor reviews repo activity</t>
         </is>
       </c>
-    </row>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+    </row>
+    <row r="3"/>
     <row r="4" ht="60" customHeight="1" s="9">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -451,6 +466,16 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Milestone 2 (Weeks 4-7): Client-Side System</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Week 8 Team Activity: Local Backend</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Average</t>
         </is>
       </c>
@@ -470,8 +495,14 @@
       <c r="D5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="5">
-        <f>IFERROR(AVERAGE(B5:D5),"")</f>
+      <c r="E5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5">
+        <f>IFERROR(AVERAGE(B5:F5),"")</f>
         <v/>
       </c>
     </row>
@@ -490,8 +521,14 @@
       <c r="D6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="5">
-        <f>IFERROR(AVERAGE(B6:D6),"")</f>
+      <c r="E6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IFERROR(AVERAGE(B6:F6),"")</f>
         <v/>
       </c>
     </row>
@@ -510,8 +547,14 @@
       <c r="D7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="5">
-        <f>IFERROR(AVERAGE(B7:D7),"")</f>
+      <c r="E7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="5">
+        <f>IFERROR(AVERAGE(B7:F7),"")</f>
         <v/>
       </c>
     </row>
@@ -530,8 +573,14 @@
       <c r="D8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="5">
-        <f>IFERROR(AVERAGE(B8:D8),"")</f>
+      <c r="E8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" s="5">
+        <f>IFERROR(AVERAGE(B8:F8),"")</f>
         <v/>
       </c>
     </row>
@@ -550,11 +599,18 @@
       <c r="D9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="5">
-        <f>IFERROR(AVERAGE(B9:D9),"")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="E9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IFERROR(AVERAGE(B9:F9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -577,19 +633,34 @@
         <f>IFERROR(AVERAGE(E5:E9),"")</f>
         <v/>
       </c>
-    </row>
+      <c r="F11" s="7">
+        <f>IFERROR(AVERAGE(F5:F9),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>IFERROR(AVERAGE(G5:G9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="9">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>To add a new activity: insert a column before "Average", title it "[Date] - [Type]: [Brief description]" (e.g., "Sep 22 - Out-of-Class: Data Dictionary Draft"), then enter each member's score 0-100.</t>
         </is>
       </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:I9">
     <cfRule type="expression" priority="2" dxfId="0">
